--- a/summary_stats/chuuchuu_summary_full_2025_april.xlsx
+++ b/summary_stats/chuuchuu_summary_full_2025_april.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M128"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,13 +525,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4">
@@ -672,19 +672,19 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6">
@@ -729,13 +729,13 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7">
@@ -780,13 +780,13 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -825,19 +825,19 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>268</v>
       </c>
       <c r="L8" t="n">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>621</v>
       </c>
     </row>
     <row r="9">
@@ -876,19 +876,19 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -927,19 +927,19 @@
         <v>110</v>
       </c>
       <c r="I10" t="n">
-        <v>157</v>
+        <v>402</v>
       </c>
       <c r="J10" t="n">
-        <v>267</v>
+        <v>512</v>
       </c>
       <c r="K10" t="n">
-        <v>39</v>
+        <v>1913</v>
       </c>
       <c r="L10" t="n">
-        <v>29</v>
+        <v>982</v>
       </c>
       <c r="M10" t="n">
-        <v>47</v>
+        <v>4054</v>
       </c>
     </row>
     <row r="11">
@@ -978,19 +978,19 @@
         <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>130</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12">
@@ -999,22 +999,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>DSB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1023,25 +1023,25 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>13744</v>
+        <v>405</v>
       </c>
       <c r="H12" t="n">
-        <v>568</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>449</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1017</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="L12" t="n">
-        <v>159</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>188</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>Deutsche Bahn</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1070,29 +1070,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1538</v>
+        <v>13744</v>
       </c>
       <c r="H13" t="n">
-        <v>39</v>
+        <v>568</v>
       </c>
       <c r="I13" t="n">
-        <v>58</v>
+        <v>1099</v>
       </c>
       <c r="J13" t="n">
-        <v>97</v>
+        <v>1667</v>
       </c>
       <c r="K13" t="n">
-        <v>216</v>
+        <v>6941</v>
       </c>
       <c r="L13" t="n">
-        <v>106</v>
+        <v>4050</v>
       </c>
       <c r="M13" t="n">
-        <v>513</v>
+        <v>12876</v>
       </c>
     </row>
     <row r="14">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>Deutsche Bahn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1121,29 +1121,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>47</v>
+        <v>1538</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="15">
@@ -1152,40 +1152,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DSB</t>
+          <t>Deutsche Bahn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>405</v>
+        <v>47</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1290,13 +1290,13 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -1386,19 +1386,19 @@
         <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="L19" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M19" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -1437,19 +1437,19 @@
         <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="L20" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="M20" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -1539,19 +1539,19 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>292</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>468</v>
       </c>
     </row>
     <row r="23">
@@ -1641,19 +1641,19 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25">
@@ -1692,19 +1692,19 @@
         <v>7</v>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>4981</v>
       </c>
       <c r="J25" t="n">
-        <v>19</v>
+        <v>4988</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1831</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>26511</v>
       </c>
     </row>
     <row r="26">
@@ -1845,19 +1845,19 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>668</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>668</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="29">
@@ -1947,19 +1947,19 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -1998,19 +1998,19 @@
         <v>43</v>
       </c>
       <c r="I31" t="n">
-        <v>43</v>
+        <v>632</v>
       </c>
       <c r="J31" t="n">
-        <v>86</v>
+        <v>675</v>
       </c>
       <c r="K31" t="n">
-        <v>84</v>
+        <v>256</v>
       </c>
       <c r="L31" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="M31" t="n">
-        <v>877</v>
+        <v>4522</v>
       </c>
     </row>
     <row r="32">
@@ -2049,10 +2049,10 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2151,19 +2151,19 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>10</v>
+        <v>8093</v>
       </c>
       <c r="J34" t="n">
-        <v>10</v>
+        <v>8093</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1986</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>61150</v>
       </c>
     </row>
     <row r="35">
@@ -2253,19 +2253,19 @@
         <v>121</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>3872</v>
       </c>
       <c r="J36" t="n">
-        <v>123</v>
+        <v>3993</v>
       </c>
       <c r="K36" t="n">
-        <v>33</v>
+        <v>865</v>
       </c>
       <c r="L36" t="n">
-        <v>13</v>
+        <v>177</v>
       </c>
       <c r="M36" t="n">
-        <v>843</v>
+        <v>32968</v>
       </c>
     </row>
     <row r="37">
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2406,19 +2406,19 @@
         <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J39" t="n">
+        <v>19</v>
+      </c>
+      <c r="K39" t="n">
+        <v>68</v>
+      </c>
+      <c r="L39" t="n">
         <v>17</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>706</v>
       </c>
     </row>
     <row r="40">
@@ -2463,13 +2463,13 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41">
@@ -2514,13 +2514,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
@@ -2559,19 +2559,19 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>632</v>
       </c>
     </row>
     <row r="43">
@@ -2616,13 +2616,13 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -2661,19 +2661,19 @@
         <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="45">
@@ -2718,13 +2718,13 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46">
@@ -2763,19 +2763,19 @@
         <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="L46" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M46" t="n">
-        <v>85</v>
+        <v>179</v>
       </c>
     </row>
     <row r="47">
@@ -2814,19 +2814,19 @@
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="J47" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="K47" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="L47" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="M47" t="n">
-        <v>46</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48">
@@ -2916,19 +2916,19 @@
         <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="J49" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="K49" t="n">
-        <v>7</v>
+        <v>189</v>
       </c>
       <c r="L49" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="M49" t="n">
-        <v>7</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="50">
@@ -2973,13 +2973,13 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51">
@@ -3018,19 +3018,19 @@
         <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>2</v>
+        <v>254</v>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>886</v>
       </c>
     </row>
     <row r="52">
@@ -3069,19 +3069,19 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J52" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>242</v>
       </c>
     </row>
     <row r="53">
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3273,19 +3273,19 @@
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J56" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>241</v>
       </c>
       <c r="L56" t="n">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>642</v>
       </c>
     </row>
     <row r="57">
@@ -3330,13 +3330,13 @@
         <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
     </row>
     <row r="58">
@@ -3375,19 +3375,19 @@
         <v>5</v>
       </c>
       <c r="I58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K58" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="L58" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="M58" t="n">
-        <v>105</v>
+        <v>688</v>
       </c>
     </row>
     <row r="59">
@@ -3426,19 +3426,19 @@
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60">
@@ -3477,19 +3477,19 @@
         <v>15</v>
       </c>
       <c r="I60" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="J60" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>10575</v>
       </c>
     </row>
     <row r="61">
@@ -3534,13 +3534,13 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62">
@@ -3630,19 +3630,19 @@
         <v>28</v>
       </c>
       <c r="I63" t="n">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="J63" t="n">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="K63" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M63" t="n">
-        <v>4</v>
+        <v>11998</v>
       </c>
     </row>
     <row r="64">
@@ -3681,19 +3681,19 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>821</v>
       </c>
     </row>
     <row r="65">
@@ -3789,13 +3789,13 @@
         <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB/NS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>INTERCITES</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4334,29 +4334,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2050</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>425</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>268</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>2033</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4365,17 +4365,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB/NS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>INTERCITES DE NUIT</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4385,29 +4385,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>248</v>
+        <v>696</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J78" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="K78" t="n">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="L78" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="M78" t="n">
-        <v>247</v>
+        <v>686</v>
       </c>
     </row>
     <row r="79">
@@ -4416,22 +4416,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB/NS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LYRIA</t>
+          <t>ECC</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4440,25 +4440,25 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1040</v>
+        <v>401</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="J79" t="n">
-        <v>5</v>
+        <v>128</v>
       </c>
       <c r="K79" t="n">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="L79" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="M79" t="n">
-        <v>1038</v>
+        <v>282</v>
       </c>
     </row>
     <row r="80">
@@ -4467,40 +4467,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB/NS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TGV</t>
+          <t>ECC</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -4518,49 +4518,49 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB/NS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TGV</t>
+          <t>ECC</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1343</v>
+        <v>317</v>
       </c>
       <c r="H81" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB/NS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TGV INOUI</t>
+          <t>ECD</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4584,34 +4584,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>14774</v>
+        <v>85</v>
       </c>
       <c r="H82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I82" t="n">
-        <v>129</v>
+        <v>12</v>
       </c>
       <c r="J82" t="n">
-        <v>146</v>
+        <v>30</v>
       </c>
       <c r="K82" t="n">
-        <v>2042</v>
+        <v>19</v>
       </c>
       <c r="L82" t="n">
-        <v>943</v>
+        <v>14</v>
       </c>
       <c r="M82" t="n">
-        <v>14714</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB/NS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TGV INOUI</t>
+          <t>ECD</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4635,34 +4635,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1140</v>
+        <v>731</v>
       </c>
       <c r="H83" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I83" t="n">
+        <v>15</v>
+      </c>
+      <c r="J83" t="n">
         <v>18</v>
       </c>
-      <c r="J83" t="n">
-        <v>25</v>
-      </c>
       <c r="K83" t="n">
-        <v>271</v>
+        <v>78</v>
       </c>
       <c r="L83" t="n">
-        <v>143</v>
+        <v>33</v>
       </c>
       <c r="M83" t="n">
-        <v>1122</v>
+        <v>541</v>
       </c>
     </row>
     <row r="84">
@@ -4671,17 +4671,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCB/NS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ECD</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4695,25 +4695,25 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>846</v>
+        <v>64</v>
       </c>
       <c r="H84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -4722,17 +4722,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>INTERCITES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4742,29 +4742,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>421</v>
+        <v>2050</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="86">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>INTERCITES DE NUIT</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4793,29 +4793,29 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G86" t="n">
+        <v>248</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>3</v>
       </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M86" t="n">
-        <v>3</v>
+        <v>247</v>
       </c>
     </row>
     <row r="87">
@@ -4824,22 +4824,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LYRIA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4848,25 +4848,25 @@
         </is>
       </c>
       <c r="G87" t="n">
+        <v>1040</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>5</v>
       </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="88">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>EXP</t>
+          <t>TGV</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4899,25 +4899,25 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="89">
@@ -4926,22 +4926,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>TGV</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4950,25 +4950,25 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>476</v>
+        <v>1343</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K89" t="n">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="L89" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="M89" t="n">
-        <v>476</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="90">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>TGV INOUI</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5001,25 +5001,25 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>283</v>
+        <v>14774</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>129</v>
       </c>
       <c r="J90" t="n">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="K90" t="n">
-        <v>153</v>
+        <v>2042</v>
       </c>
       <c r="L90" t="n">
-        <v>75</v>
+        <v>943</v>
       </c>
       <c r="M90" t="n">
-        <v>283</v>
+        <v>14714</v>
       </c>
     </row>
     <row r="91">
@@ -5028,17 +5028,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>TGV INOUI</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5052,25 +5052,25 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>6595</v>
+        <v>1140</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I91" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J91" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K91" t="n">
-        <v>2071</v>
+        <v>271</v>
       </c>
       <c r="L91" t="n">
-        <v>942</v>
+        <v>143</v>
       </c>
       <c r="M91" t="n">
-        <v>6592</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="92">
@@ -5084,44 +5084,44 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>82</v>
+        <v>846</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J92" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K92" t="n">
-        <v>49</v>
+        <v>180</v>
       </c>
       <c r="L92" t="n">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="M92" t="n">
-        <v>77</v>
+        <v>837</v>
       </c>
     </row>
     <row r="93">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5150,29 +5150,29 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>2819</v>
+        <v>421</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>2811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ICN</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5201,11 +5201,11 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>529</v>
+        <v>3</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -5217,13 +5217,13 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>529</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5252,29 +5252,29 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>EXP</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5303,29 +5303,29 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>6256</v>
+        <v>26</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>171</v>
+        <v>13</v>
       </c>
       <c r="L96" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="M96" t="n">
-        <v>6212</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NCL</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5354,29 +5354,29 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>12</v>
+        <v>476</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>5</v>
+        <v>222</v>
       </c>
       <c r="L97" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="M97" t="n">
-        <v>8</v>
+        <v>476</v>
       </c>
     </row>
     <row r="98">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NCL</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5405,29 +5405,29 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G98" t="n">
+        <v>283</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
         <v>2</v>
       </c>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>283</v>
       </c>
     </row>
     <row r="99">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5451,34 +5451,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>217367</v>
+        <v>6595</v>
       </c>
       <c r="H99" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>4121</v>
+        <v>12</v>
       </c>
       <c r="J99" t="n">
-        <v>4156</v>
+        <v>12</v>
       </c>
       <c r="K99" t="n">
-        <v>22579</v>
+        <v>2071</v>
       </c>
       <c r="L99" t="n">
-        <v>5251</v>
+        <v>942</v>
       </c>
       <c r="M99" t="n">
-        <v>215098</v>
+        <v>6592</v>
       </c>
     </row>
     <row r="100">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5502,34 +5502,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1797</v>
+        <v>82</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K100" t="n">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="L100" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M100" t="n">
-        <v>1794</v>
+        <v>77</v>
       </c>
     </row>
     <row r="101">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5558,29 +5558,29 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>2819</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="102">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BUS</t>
+          <t>ICN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5609,11 +5609,11 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>2943</v>
+        <v>529</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -5625,13 +5625,13 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M102" t="n">
-        <v>51</v>
+        <v>529</v>
       </c>
     </row>
     <row r="103">
@@ -5640,17 +5640,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BUS</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5660,29 +5660,29 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>395</v>
+        <v>3</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5715,25 +5715,25 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>321</v>
+        <v>6256</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>6212</v>
       </c>
     </row>
     <row r="105">
@@ -5742,17 +5742,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>NCL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5766,25 +5766,25 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>759</v>
+        <v>12</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106">
@@ -5793,17 +5793,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>NCL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2021</v>
+        <v>2</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5868,25 +5868,25 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>217367</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>4121</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>4156</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>22579</v>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>5251</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>215098</v>
       </c>
     </row>
     <row r="108">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5919,25 +5919,25 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>582</v>
+        <v>1797</v>
       </c>
       <c r="H108" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J108" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="109">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DBK</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>BUS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>2943</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -6033,13 +6033,13 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="111">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>BUS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6072,25 +6072,25 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>963</v>
+        <v>395</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>716</v>
+        <v>395</v>
       </c>
     </row>
     <row r="112">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ECC</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6123,25 +6123,25 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>401</v>
+        <v>321</v>
       </c>
       <c r="H112" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>192</v>
+        <v>321</v>
       </c>
     </row>
     <row r="113">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ECC</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>64</v>
+        <v>759</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -6192,7 +6192,7 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>759</v>
       </c>
     </row>
     <row r="114">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ECC</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6225,16 +6225,16 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>317</v>
+        <v>2021</v>
       </c>
       <c r="H114" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -6243,7 +6243,7 @@
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="115">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ECD</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6276,25 +6276,25 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ECD</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6327,25 +6327,25 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>731</v>
+        <v>582</v>
       </c>
       <c r="H116" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I116" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K116" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L116" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M116" t="n">
-        <v>541</v>
+        <v>572</v>
       </c>
     </row>
     <row r="117">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ECD</t>
+          <t>DBK</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -6390,13 +6390,13 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6429,25 +6429,25 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>14</v>
+        <v>267</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
     </row>
     <row r="119">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GEP</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6480,7 +6480,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -6492,13 +6492,13 @@
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6549,7 +6549,7 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="121">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>GEP</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -6600,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="122">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6633,25 +6633,25 @@
         </is>
       </c>
       <c r="G122" t="n">
+        <v>141</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
         <v>1</v>
       </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
     </row>
     <row r="123">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6684,16 +6684,16 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>9983</v>
+        <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6735,25 +6735,25 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>20</v>
+        <v>9983</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>9920</v>
       </c>
     </row>
     <row r="125">
@@ -6767,12 +6767,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>1318</v>
+        <v>20</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -6804,7 +6804,7 @@
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>50</v>
+        <v>1318</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -6855,7 +6855,7 @@
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="127">
@@ -6864,17 +6864,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Westbahn</t>
+          <t>UNKNOWN_OPERATOR</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6884,11 +6884,11 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>1366</v>
+        <v>50</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -6906,7 +6906,7 @@
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="128">
@@ -6925,39 +6925,90 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>1366</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>26</v>
+      </c>
+      <c r="L128" t="n">
+        <v>13</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Westbahn</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
           <t>international</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G128" t="n">
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
         <v>4</v>
       </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" t="n">
-        <v>0</v>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/summary_stats/chuuchuu_summary_full_2025_april.xlsx
+++ b/summary_stats/chuuchuu_summary_full_2025_april.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>Ceske Drahy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -525,13 +525,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>142</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -540,12 +540,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>Ceske Drahy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -564,25 +564,25 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>149</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
-        <v>149</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -596,7 +596,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6">
@@ -717,25 +717,25 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L6" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="M6" t="n">
-        <v>397</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7">
@@ -768,25 +768,25 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -819,25 +819,25 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>657</v>
+        <v>770</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="J8" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="K8" t="n">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="L8" t="n">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="M8" t="n">
-        <v>621</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9">
@@ -870,25 +870,25 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
       <c r="K9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L9" t="n">
         <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -921,25 +921,25 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4292</v>
+        <v>4217</v>
       </c>
       <c r="H10" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I10" t="n">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J10" t="n">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="K10" t="n">
-        <v>1913</v>
+        <v>1852</v>
       </c>
       <c r="L10" t="n">
-        <v>982</v>
+        <v>936</v>
       </c>
       <c r="M10" t="n">
-        <v>4054</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="11">
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>423</v>
+        <v>899</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="K11" t="n">
-        <v>130</v>
+        <v>365</v>
       </c>
       <c r="L11" t="n">
-        <v>87</v>
+        <v>213</v>
       </c>
       <c r="M11" t="n">
-        <v>249</v>
+        <v>845</v>
       </c>
     </row>
     <row r="12">
@@ -999,7 +999,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DSB</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1023,25 +1023,25 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>405</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deutsche Bahn</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1070,29 +1070,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>13744</v>
+        <v>13399</v>
       </c>
       <c r="H13" t="n">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="I13" t="n">
-        <v>1099</v>
+        <v>1080</v>
       </c>
       <c r="J13" t="n">
-        <v>1667</v>
+        <v>1644</v>
       </c>
       <c r="K13" t="n">
-        <v>6941</v>
+        <v>6722</v>
       </c>
       <c r="L13" t="n">
-        <v>4050</v>
+        <v>3860</v>
       </c>
       <c r="M13" t="n">
-        <v>12876</v>
+        <v>12398</v>
       </c>
     </row>
     <row r="14">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deutsche Bahn</t>
+          <t>DB/NS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1121,29 +1121,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1538</v>
+        <v>418</v>
       </c>
       <c r="H14" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="J14" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="K14" t="n">
-        <v>448</v>
+        <v>205</v>
       </c>
       <c r="L14" t="n">
-        <v>241</v>
+        <v>123</v>
       </c>
       <c r="M14" t="n">
-        <v>1072</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deutsche Bahn</t>
+          <t>DB/OEBB</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1172,29 +1172,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>47</v>
+        <v>676</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>624</v>
       </c>
     </row>
     <row r="16">
@@ -1203,22 +1203,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>European Sleeper</t>
+          <t>DB/SBB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1227,25 +1227,25 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>1005</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>207</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>238</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>355</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>193</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>864</v>
       </c>
     </row>
     <row r="17">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>European Sleeper</t>
+          <t>DB/SNCB</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>25</v>
+        <v>425</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="M17" t="n">
-        <v>25</v>
+        <v>406</v>
       </c>
     </row>
     <row r="18">
@@ -1305,22 +1305,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>European Sleeper</t>
+          <t>DB/SNCF</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1329,25 +1329,25 @@
         </is>
       </c>
       <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
         <v>4</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1356,22 +1356,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eurostar</t>
+          <t>DSB</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1380,25 +1380,25 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>47</v>
+        <v>401</v>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="L19" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>29</v>
+        <v>399</v>
       </c>
     </row>
     <row r="20">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Eurostar</t>
+          <t>European Sleeper</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1431,25 +1431,25 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1458,22 +1458,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Eurostar</t>
+          <t>European Sleeper</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1482,25 +1482,25 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -1509,17 +1509,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Flixtrain</t>
+          <t>European Sleeper</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FLX</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>470</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HZ</t>
+          <t>Eurostar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1575,34 +1575,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>3389</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>874</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="24">
@@ -1611,22 +1611,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MAV</t>
+          <t>Eurostar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1635,25 +1635,25 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>Flixtrain</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>FLX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1686,25 +1686,25 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>31001</v>
+        <v>466</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>4981</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>4988</v>
+        <v>33</v>
       </c>
       <c r="K25" t="n">
-        <v>1831</v>
+        <v>289</v>
       </c>
       <c r="L25" t="n">
-        <v>360</v>
+        <v>185</v>
       </c>
       <c r="M25" t="n">
-        <v>26511</v>
+        <v>461</v>
       </c>
     </row>
     <row r="26">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>Flixtrain</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>FLX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1737,25 +1737,25 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H26" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
@@ -1764,17 +1764,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>HZ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1784,11 +1784,11 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>HZ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ICD</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1835,29 +1835,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2754</v>
+        <v>43</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>668</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>668</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>302</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>2272</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
@@ -1866,17 +1866,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MAV</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ICD</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1917,17 +1917,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>MAV</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1937,29 +1937,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>15</v>
+      </c>
+      <c r="L30" t="n">
         <v>6</v>
       </c>
-      <c r="J30" t="n">
-        <v>6</v>
-      </c>
-      <c r="K30" t="n">
-        <v>5</v>
-      </c>
-      <c r="L30" t="n">
-        <v>2</v>
-      </c>
       <c r="M30" t="n">
-        <v>14</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1988,29 +1988,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>5072</v>
+        <v>30988</v>
       </c>
       <c r="H31" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>632</v>
+        <v>4981</v>
       </c>
       <c r="J31" t="n">
-        <v>675</v>
+        <v>4981</v>
       </c>
       <c r="K31" t="n">
-        <v>256</v>
+        <v>1726</v>
       </c>
       <c r="L31" t="n">
-        <v>68</v>
+        <v>305</v>
       </c>
       <c r="M31" t="n">
-        <v>4522</v>
+        <v>26404</v>
       </c>
     </row>
     <row r="32">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2039,20 +2039,20 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>178</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>ICD</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2090,29 +2090,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>313</v>
+        <v>2754</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>668</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>668</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="34">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2145,25 +2145,25 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>68525</v>
+        <v>17</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>8093</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
-        <v>8093</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
-        <v>1986</v>
+        <v>5</v>
       </c>
       <c r="L34" t="n">
-        <v>283</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>61150</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2196,25 +2196,25 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>11</v>
+        <v>3532</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="36">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2247,25 +2247,25 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>36730</v>
+        <v>178</v>
       </c>
       <c r="H36" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>3872</v>
+        <v>178</v>
       </c>
       <c r="J36" t="n">
-        <v>3993</v>
+        <v>178</v>
       </c>
       <c r="K36" t="n">
-        <v>865</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>32968</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2298,25 +2298,25 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>213</v>
+        <v>68525</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>213</v>
+        <v>8093</v>
       </c>
       <c r="J37" t="n">
-        <v>213</v>
+        <v>8093</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1879</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>61040</v>
       </c>
     </row>
     <row r="38">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2349,25 +2349,25 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1064</v>
+        <v>34913</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3742</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>3743</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>31343</v>
       </c>
     </row>
     <row r="39">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OEBB</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2396,29 +2396,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>723</v>
+        <v>197</v>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>15</v>
+        <v>197</v>
       </c>
       <c r="J39" t="n">
-        <v>19</v>
+        <v>197</v>
       </c>
       <c r="K39" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>706</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2451,25 +2451,25 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>282</v>
+        <v>717</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="K40" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="L40" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M40" t="n">
-        <v>281</v>
+        <v>700</v>
       </c>
     </row>
     <row r="41">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2502,25 +2502,25 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>22</v>
+        <v>399</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M41" t="n">
-        <v>22</v>
+        <v>399</v>
       </c>
     </row>
     <row r="42">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2553,25 +2553,25 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>632</v>
+        <v>22</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>187</v>
+        <v>8</v>
       </c>
       <c r="L42" t="n">
-        <v>128</v>
+        <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>632</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2600,29 +2600,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>822</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>243</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="M43" t="n">
-        <v>5</v>
+        <v>812</v>
       </c>
     </row>
     <row r="44">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2655,25 +2655,25 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1615</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2702,11 +2702,11 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>113</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2718,13 +2718,13 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>2</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>113</v>
       </c>
     </row>
     <row r="46">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2753,29 +2753,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>188</v>
+        <v>66</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="L46" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="M46" t="n">
-        <v>179</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2808,25 +2808,25 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>319</v>
+        <v>1601</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="K47" t="n">
-        <v>62</v>
+        <v>163</v>
       </c>
       <c r="L47" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="M47" t="n">
-        <v>291</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="48">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2859,25 +2859,25 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>35</v>
+        <v>177</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2910,25 +2910,25 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1845</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2961,25 +2961,25 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="L50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M50" t="n">
-        <v>115</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51">
@@ -2993,17 +2993,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RJX</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3012,25 +3012,25 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>917</v>
+        <v>773</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K51" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="L51" t="n">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="M51" t="n">
-        <v>886</v>
+        <v>764</v>
       </c>
     </row>
     <row r="52">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>RJX</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3063,25 +3063,25 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>246</v>
+        <v>2</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3090,17 +3090,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ouigo</t>
+          <t>OEBB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OTC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3110,29 +3110,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>119</v>
+        <v>1834</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="K53" t="n">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="L53" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="M53" t="n">
-        <v>117</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="54">
@@ -3141,17 +3141,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ouigo</t>
+          <t>OEBB</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OUIGO</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3161,29 +3161,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1798</v>
+        <v>509</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K54" t="n">
-        <v>269</v>
+        <v>162</v>
       </c>
       <c r="L54" t="n">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="M54" t="n">
-        <v>1795</v>
+        <v>507</v>
       </c>
     </row>
     <row r="55">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PKP</t>
+          <t>OEBB</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3243,22 +3243,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PKP Intercity</t>
+          <t>OEBB</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>RJX</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3267,25 +3267,25 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>644</v>
+        <v>866</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="K56" t="n">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="L56" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M56" t="n">
-        <v>642</v>
+        <v>852</v>
       </c>
     </row>
     <row r="57">
@@ -3294,22 +3294,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SBB</t>
+          <t>OEBB</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>RJX</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3318,25 +3318,25 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>206</v>
+        <v>927</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>409</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="M57" t="n">
-        <v>206</v>
+        <v>918</v>
       </c>
     </row>
     <row r="58">
@@ -3345,22 +3345,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SBB</t>
+          <t>OEBB</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>RJX</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3369,25 +3369,25 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>713</v>
+        <v>7</v>
       </c>
       <c r="H58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3396,17 +3396,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SBB</t>
+          <t>Other CH operators</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3420,25 +3420,25 @@
         </is>
       </c>
       <c r="G59" t="n">
+        <v>9930</v>
+      </c>
+      <c r="H59" t="n">
+        <v>7</v>
+      </c>
+      <c r="I59" t="n">
         <v>61</v>
       </c>
-      <c r="H59" t="n">
-        <v>1</v>
-      </c>
-      <c r="I59" t="n">
-        <v>2</v>
-      </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="K59" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="L59" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>59</v>
+        <v>9867</v>
       </c>
     </row>
     <row r="60">
@@ -3447,17 +3447,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SBB</t>
+          <t>Other CH operators</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3467,29 +3467,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>10716</v>
+        <v>20</v>
       </c>
       <c r="H60" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>10575</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -3498,17 +3498,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SBB</t>
+          <t>Other CH operators</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3518,11 +3518,11 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -3534,13 +3534,13 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SBB</t>
+          <t>Ouigo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>OTC</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3569,29 +3569,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63">
@@ -3600,12 +3600,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SBB</t>
+          <t>Ouigo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>OUIGO</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>12134</v>
+        <v>1735</v>
       </c>
       <c r="H63" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="J63" t="n">
-        <v>176</v>
+        <v>7</v>
       </c>
       <c r="K63" t="n">
-        <v>13</v>
+        <v>244</v>
       </c>
       <c r="L63" t="n">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="M63" t="n">
-        <v>11998</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="64">
@@ -3651,22 +3651,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SBB</t>
+          <t>Ouigo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>OUIGO</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3675,25 +3675,25 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>836</v>
+        <v>59</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -3702,17 +3702,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SBB</t>
+          <t>PKP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3722,11 +3722,11 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SJ</t>
+          <t>PKP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3777,25 +3777,25 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>45</v>
+        <v>632</v>
       </c>
       <c r="H66" t="n">
         <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K66" t="n">
-        <v>19</v>
+        <v>250</v>
       </c>
       <c r="L66" t="n">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="M66" t="n">
-        <v>43</v>
+        <v>627</v>
       </c>
     </row>
     <row r="67">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SNCB</t>
+          <t>PKP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3828,25 +3828,25 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>24398</v>
+        <v>4</v>
       </c>
       <c r="H67" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>2909</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>764</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>24193</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SNCB</t>
+          <t>PKP</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3879,25 +3879,25 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1989</v>
+        <v>53</v>
       </c>
       <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
         <v>2</v>
       </c>
-      <c r="I68" t="n">
-        <v>39</v>
-      </c>
       <c r="J68" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="L68" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="M68" t="n">
-        <v>1964</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SNCB</t>
+          <t>Panorama Express</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>5</v>
+        <v>1313</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="70">
@@ -3957,17 +3957,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SNCB</t>
+          <t>Panorama Express</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3981,25 +3981,25 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>14516</v>
+        <v>49</v>
       </c>
       <c r="H70" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>1164</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>14454</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71">
@@ -4008,17 +4008,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SNCB</t>
+          <t>SBB</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4028,29 +4028,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>2446</v>
+        <v>51</v>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>2437</v>
+        <v>51</v>
       </c>
     </row>
     <row r="72">
@@ -4059,17 +4059,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SNCB</t>
+          <t>SBB</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4079,29 +4079,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3417</v>
+        <v>841</v>
       </c>
       <c r="H72" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="I72" t="n">
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="K72" t="n">
-        <v>370</v>
+        <v>241</v>
       </c>
       <c r="L72" t="n">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="M72" t="n">
-        <v>3377</v>
+        <v>828</v>
       </c>
     </row>
     <row r="73">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SNCB</t>
+          <t>SBB</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>ECE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4134,25 +4134,25 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>63</v>
+        <v>215</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="M73" t="n">
-        <v>62</v>
+        <v>212</v>
       </c>
     </row>
     <row r="74">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SNCB</t>
+          <t>SBB</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4181,29 +4181,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>22664</v>
+        <v>10649</v>
       </c>
       <c r="H74" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="I74" t="n">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="J74" t="n">
-        <v>257</v>
+        <v>154</v>
       </c>
       <c r="K74" t="n">
-        <v>1702</v>
+        <v>20</v>
       </c>
       <c r="L74" t="n">
-        <v>355</v>
+        <v>7</v>
       </c>
       <c r="M74" t="n">
-        <v>22531</v>
+        <v>10507</v>
       </c>
     </row>
     <row r="75">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SNCB</t>
+          <t>SBB</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4232,29 +4232,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1699</v>
+        <v>749</v>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="I75" t="n">
+        <v>40</v>
+      </c>
+      <c r="J75" t="n">
         <v>74</v>
       </c>
-      <c r="J75" t="n">
-        <v>76</v>
-      </c>
       <c r="K75" t="n">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="L75" t="n">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="M75" t="n">
-        <v>1678</v>
+        <v>700</v>
       </c>
     </row>
     <row r="76">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SNCB</t>
+          <t>SBB</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4283,20 +4283,20 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G76" t="n">
+        <v>8</v>
+      </c>
+      <c r="H76" t="n">
         <v>1</v>
       </c>
-      <c r="H76" t="n">
-        <v>0</v>
-      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -4314,12 +4314,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SNCB/NS</t>
+          <t>SBB</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4334,29 +4334,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>12067</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M77" t="n">
-        <v>1</v>
+        <v>11928</v>
       </c>
     </row>
     <row r="78">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SNCB/NS</t>
+          <t>SBB</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4385,29 +4385,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>696</v>
+        <v>830</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K78" t="n">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="L78" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>686</v>
+        <v>814</v>
       </c>
     </row>
     <row r="79">
@@ -4416,17 +4416,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SNCB/NS</t>
+          <t>SBB</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ECC</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4436,29 +4436,29 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>401</v>
+        <v>4</v>
       </c>
       <c r="H79" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SNCB/NS</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ECC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4491,25 +4491,25 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="81">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SNCB/NS</t>
+          <t>SNCB</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ECC</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4538,29 +4538,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>317</v>
+        <v>24351</v>
       </c>
       <c r="H81" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>474</v>
       </c>
       <c r="J81" t="n">
-        <v>11</v>
+        <v>548</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>2754</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>622</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>24008</v>
       </c>
     </row>
     <row r="82">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SNCB/NS</t>
+          <t>SNCB</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ECD</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4589,29 +4589,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>85</v>
+        <v>1991</v>
       </c>
       <c r="H82" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I82" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="J82" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K82" t="n">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="L82" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="M82" t="n">
-        <v>45</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="83">
@@ -4620,17 +4620,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SNCB/NS</t>
+          <t>SNCB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ECD</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4640,29 +4640,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>731</v>
+        <v>2</v>
       </c>
       <c r="H83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I83" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K83" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>541</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -4671,17 +4671,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SNCB/NS</t>
+          <t>SNCB</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ECD</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4695,25 +4695,25 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>64</v>
+        <v>14508</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1136</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>14422</v>
       </c>
     </row>
     <row r="85">
@@ -4722,17 +4722,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>INTERCITES</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4742,29 +4742,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>2050</v>
+        <v>2443</v>
       </c>
       <c r="H85" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I85" t="n">
         <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K85" t="n">
-        <v>425</v>
+        <v>104</v>
       </c>
       <c r="L85" t="n">
-        <v>268</v>
+        <v>17</v>
       </c>
       <c r="M85" t="n">
-        <v>2033</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="86">
@@ -4773,17 +4773,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>INTERCITES DE NUIT</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4793,29 +4793,29 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>248</v>
+        <v>3</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -4824,22 +4824,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LYRIA</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4848,25 +4848,25 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1040</v>
+        <v>3417</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="K87" t="n">
-        <v>112</v>
+        <v>363</v>
       </c>
       <c r="L87" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="M87" t="n">
-        <v>1038</v>
+        <v>3371</v>
       </c>
     </row>
     <row r="88">
@@ -4875,49 +4875,49 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TGV</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="89">
@@ -4926,49 +4926,49 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TGV</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1343</v>
+        <v>22648</v>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="I89" t="n">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="J89" t="n">
-        <v>18</v>
+        <v>254</v>
       </c>
       <c r="K89" t="n">
-        <v>210</v>
+        <v>1628</v>
       </c>
       <c r="L89" t="n">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="M89" t="n">
-        <v>1336</v>
+        <v>22461</v>
       </c>
     </row>
     <row r="90">
@@ -4977,49 +4977,49 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TGV INOUI</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>14774</v>
+        <v>1702</v>
       </c>
       <c r="H90" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I90" t="n">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="J90" t="n">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="K90" t="n">
-        <v>2042</v>
+        <v>235</v>
       </c>
       <c r="L90" t="n">
-        <v>943</v>
+        <v>34</v>
       </c>
       <c r="M90" t="n">
-        <v>14714</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="91">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SNCF</t>
+          <t>SNCB/NS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TGV INOUI</t>
+          <t>EUROCITY</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5043,34 +5043,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>1140</v>
+        <v>730</v>
       </c>
       <c r="H91" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="J91" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="K91" t="n">
-        <v>271</v>
+        <v>125</v>
       </c>
       <c r="L91" t="n">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="M91" t="n">
-        <v>1122</v>
+        <v>684</v>
       </c>
     </row>
     <row r="92">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCB/NS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EUROCITY DIRECT</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5103,25 +5103,25 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>846</v>
+        <v>6</v>
       </c>
       <c r="H92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>837</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
@@ -5130,17 +5130,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCB/NS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EUROCITY DIRECT</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5154,25 +5154,25 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>421</v>
+        <v>768</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>745</v>
       </c>
     </row>
     <row r="94">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5196,34 +5196,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M94" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
@@ -5232,49 +5232,49 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>5</v>
+        <v>721</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
     </row>
     <row r="96">
@@ -5283,22 +5283,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>EXP</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5307,25 +5307,25 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>INTERCITES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5358,25 +5358,25 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>476</v>
+        <v>2021</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K97" t="n">
-        <v>222</v>
+        <v>394</v>
       </c>
       <c r="L97" t="n">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="M97" t="n">
-        <v>476</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="98">
@@ -5385,17 +5385,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>INTERCITES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5409,25 +5409,25 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>283</v>
+        <v>27</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5436,12 +5436,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>INTERCITES DE NUIT</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5460,25 +5460,25 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>6595</v>
+        <v>141</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K99" t="n">
-        <v>2071</v>
+        <v>29</v>
       </c>
       <c r="L99" t="n">
-        <v>942</v>
+        <v>18</v>
       </c>
       <c r="M99" t="n">
-        <v>6592</v>
+        <v>140</v>
       </c>
     </row>
     <row r="100">
@@ -5487,22 +5487,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>INTERCITES DE NUIT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5511,25 +5511,25 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>LYRIA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5562,25 +5562,25 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>2819</v>
+        <v>60</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>786</v>
+        <v>1</v>
       </c>
       <c r="L101" t="n">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>2811</v>
+        <v>60</v>
       </c>
     </row>
     <row r="102">
@@ -5589,22 +5589,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ICN</t>
+          <t>LYRIA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5613,25 +5613,25 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>529</v>
+        <v>1027</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K102" t="n">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="L102" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="M102" t="n">
-        <v>529</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="103">
@@ -5640,22 +5640,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>LYRIA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5664,25 +5664,25 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>TGV INOUI</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5706,34 +5706,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>6256</v>
+        <v>13974</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I104" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="J104" t="n">
         <v>110</v>
       </c>
       <c r="K104" t="n">
-        <v>171</v>
+        <v>1723</v>
       </c>
       <c r="L104" t="n">
-        <v>42</v>
+        <v>768</v>
       </c>
       <c r="M104" t="n">
-        <v>6212</v>
+        <v>13941</v>
       </c>
     </row>
     <row r="105">
@@ -5742,49 +5742,49 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NCL</t>
+          <t>TGV INOUI</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>12</v>
+        <v>808</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I105" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J105" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K105" t="n">
-        <v>5</v>
+        <v>194</v>
       </c>
       <c r="L105" t="n">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="M105" t="n">
-        <v>8</v>
+        <v>796</v>
       </c>
     </row>
     <row r="106">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NCL</t>
+          <t>TGV INOUI</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5808,25 +5808,25 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>1094</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -5844,49 +5844,49 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Trenitalia</t>
+          <t>SNCF/DB</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>TGV</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>217367</v>
+        <v>23</v>
       </c>
       <c r="H107" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="I107" t="n">
-        <v>4121</v>
+        <v>4</v>
       </c>
       <c r="J107" t="n">
-        <v>4156</v>
+        <v>5</v>
       </c>
       <c r="K107" t="n">
-        <v>22579</v>
+        <v>7</v>
       </c>
       <c r="L107" t="n">
-        <v>5251</v>
+        <v>2</v>
       </c>
       <c r="M107" t="n">
-        <v>215098</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5919,25 +5919,25 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1797</v>
+        <v>137</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="L108" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="M108" t="n">
-        <v>1794</v>
+        <v>137</v>
       </c>
     </row>
     <row r="109">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5970,25 +5970,25 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>612</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>597</v>
       </c>
     </row>
     <row r="110">
@@ -5997,17 +5997,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BUS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2943</v>
+        <v>1</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -6033,13 +6033,13 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>2943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BUS</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6072,7 +6072,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>395</v>
+        <v>2</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -6084,13 +6084,13 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>395</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6123,25 +6123,25 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>321</v>
+        <v>27</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M112" t="n">
-        <v>321</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113">
@@ -6150,17 +6150,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>EXP</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6170,29 +6170,29 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>759</v>
+        <v>26</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M113" t="n">
-        <v>759</v>
+        <v>24</v>
       </c>
     </row>
     <row r="114">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>2021</v>
+        <v>476</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -6237,13 +6237,13 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="M114" t="n">
-        <v>2021</v>
+        <v>476</v>
       </c>
     </row>
     <row r="115">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6272,29 +6272,29 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>283</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M115" t="n">
-        <v>1</v>
+        <v>283</v>
       </c>
     </row>
     <row r="116">
@@ -6303,49 +6303,49 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>582</v>
+        <v>6594</v>
       </c>
       <c r="H116" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J116" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K116" t="n">
-        <v>74</v>
+        <v>2067</v>
       </c>
       <c r="L116" t="n">
-        <v>34</v>
+        <v>939</v>
       </c>
       <c r="M116" t="n">
-        <v>572</v>
+        <v>6588</v>
       </c>
     </row>
     <row r="117">
@@ -6354,49 +6354,49 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DBK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="L117" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="M117" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
     </row>
     <row r="118">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6425,29 +6425,29 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>267</v>
+        <v>2818</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J118" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K118" t="n">
-        <v>31</v>
+        <v>784</v>
       </c>
       <c r="L118" t="n">
-        <v>15</v>
+        <v>333</v>
       </c>
       <c r="M118" t="n">
-        <v>262</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="119">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6476,11 +6476,11 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -6492,13 +6492,13 @@
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GEP</t>
+          <t>ICN</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6527,11 +6527,11 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>56</v>
+        <v>529</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -6543,13 +6543,13 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M120" t="n">
-        <v>56</v>
+        <v>529</v>
       </c>
     </row>
     <row r="121">
@@ -6558,17 +6558,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GEP</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6578,29 +6578,29 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -6609,17 +6609,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6633,25 +6633,25 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>141</v>
+        <v>6256</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="K122" t="n">
-        <v>9</v>
+        <v>159</v>
       </c>
       <c r="L122" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="M122" t="n">
-        <v>139</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="123">
@@ -6660,17 +6660,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>NCL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6684,25 +6684,25 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="124">
@@ -6711,17 +6711,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>NCL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6735,25 +6735,25 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>9983</v>
+        <v>2</v>
       </c>
       <c r="H124" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>9920</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -6762,17 +6762,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6786,25 +6786,25 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>20</v>
+        <v>218052</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>4119</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>4154</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>21851</v>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>4851</v>
       </c>
       <c r="M125" t="n">
-        <v>20</v>
+        <v>214909</v>
       </c>
     </row>
     <row r="126">
@@ -6813,17 +6813,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>international</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6837,25 +6837,25 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>1318</v>
+        <v>1112</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M126" t="n">
-        <v>1318</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="127">
@@ -6864,17 +6864,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>UNKNOWN_OPERATOR</t>
+          <t>Trenitalia</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>international</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -6906,7 +6906,7 @@
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Westbahn</t>
+          <t>UNKNOWN_OPERATOR</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>BUS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6935,11 +6935,11 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1366</v>
+        <v>3251</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -6951,13 +6951,13 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L128" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M128" t="n">
-        <v>1366</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="129">
@@ -6966,49 +6966,1057 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>BUS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>1174</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>13</v>
+      </c>
+      <c r="L129" t="n">
+        <v>10</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>BUS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>4</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>2011</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>450</v>
+      </c>
+      <c r="H134" t="n">
+        <v>10</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" t="n">
+        <v>11</v>
+      </c>
+      <c r="K134" t="n">
+        <v>80</v>
+      </c>
+      <c r="L134" t="n">
+        <v>38</v>
+      </c>
+      <c r="M134" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>DBK</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>2</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>129</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>6</v>
+      </c>
+      <c r="J136" t="n">
+        <v>6</v>
+      </c>
+      <c r="K136" t="n">
+        <v>6</v>
+      </c>
+      <c r="L136" t="n">
+        <v>3</v>
+      </c>
+      <c r="M136" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>GEP</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>56</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>GEP</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>56</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>3</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>195</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="n">
+        <v>10</v>
+      </c>
+      <c r="L141" t="n">
+        <v>6</v>
+      </c>
+      <c r="M141" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>65</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>3</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>8</v>
+      </c>
+      <c r="H144" t="n">
+        <v>3</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>3</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>5</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1</v>
+      </c>
+      <c r="L145" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>74</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>74</v>
+      </c>
+      <c r="J146" t="n">
+        <v>74</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>UNKNOWN_OPERATOR</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>3</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
           <t>Westbahn</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>1355</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>26</v>
+      </c>
+      <c r="L148" t="n">
+        <v>12</v>
+      </c>
+      <c r="M148" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Westbahn</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
         <is>
           <t>international</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
-        <v>4</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="n">
-        <v>1</v>
-      </c>
-      <c r="L129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" t="n">
-        <v>4</v>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>324</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>5</v>
+      </c>
+      <c r="J149" t="n">
+        <v>5</v>
+      </c>
+      <c r="K149" t="n">
+        <v>100</v>
+      </c>
+      <c r="L149" t="n">
+        <v>35</v>
+      </c>
+      <c r="M149" t="n">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
